--- a/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/MPJ_DAE_2026_T1_Chubut.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/MPJ_DAE_2026_T1_Chubut.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/MPJ_DAE_2026_T1_Chubut.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/MPJ_DAE_2026_T1_Chubut.xlsx
@@ -267,7 +267,7 @@
         <t>ID del Niño, niña o Adolescente
 Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -623,7 +623,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -1323,9 +1323,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>42.84</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>29.65</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>27.51</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>68.37</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45767</v>
+        <v>45768</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>64.26000000000001</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45800</v>
+        <v>45801</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>87.37</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>28.57</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45702</v>
+        <v>45703</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>19.83</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>69.95999999999999</v>
       </c>
       <c r="AI12" s="5" t="n">
-        <v>46075</v>
+        <v>46076</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45788</v>
+        <v>45789</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>25.38</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45857</v>
+        <v>45858</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>83.54000000000001</v>
       </c>
       <c r="AI14" s="5" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>34.02</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>56.43</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>33.5</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45765</v>
+        <v>45766</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>43.7</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>32.9</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>40.57</v>
       </c>
       <c r="AI20" s="5" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>25.48</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>83.45999999999999</v>
       </c>
       <c r="AI22" s="5" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45808</v>
+        <v>45809</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>90.79000000000001</v>
       </c>
       <c r="AI23" s="5" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>4.07</v>
       </c>
       <c r="AI24" s="5" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>94.20999999999999</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>46018</v>
+        <v>46019</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45843</v>
+        <v>45844</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>16.15</v>
       </c>
       <c r="AI26" s="5" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>88.15000000000001</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45757</v>
+        <v>45758</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>35.83</v>
       </c>
       <c r="AI28" s="5" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45977</v>
+        <v>45978</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>28.16</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>56.25</v>
       </c>
       <c r="AI30" s="5" t="n">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>69.25</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45807</v>
+        <v>45808</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>50.55</v>
       </c>
       <c r="AI32" s="5" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>16.92</v>
       </c>
       <c r="AI33" s="5" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -8227,9 +8227,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -8415,7 +8415,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AD4" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>0.2604166666666667</v>
@@ -8601,7 +8601,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD5" s="8" t="n">
         <v>0.6145833333333334</v>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>0.8854166666666666</v>
@@ -8795,7 +8795,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AD6" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="AK6" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -8977,7 +8977,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="AD7" s="8" t="n">
         <v>0.4791666666666667</v>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="AK7" s="8" t="n">
         <v>0.7395833333333334</v>
@@ -9172,7 +9172,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46102</v>
+        <v>46103</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="AD8" s="8" t="n">
         <v>0.8541666666666666</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>0.78125</v>
@@ -9363,7 +9363,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="AD9" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="AD10" s="8" t="n">
         <v>0.7083333333333334</v>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="AK10" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="AD11" s="8" t="n">
         <v>0.96875</v>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="AK11" s="8" t="n">
         <v>0.9895833333333334</v>
@@ -9935,7 +9935,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="AD12" s="8" t="n">
         <v>0.5</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>0.34375</v>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="AD14" s="8" t="n">
         <v>0.9375</v>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="AK14" s="8" t="n">
         <v>0.96875</v>
@@ -10490,7 +10490,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45711</v>
+        <v>45712</v>
       </c>
       <c r="AD15" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>0.3125</v>
@@ -10680,7 +10680,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AD16" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AK16" s="8" t="n">
         <v>0.75</v>
@@ -10879,7 +10879,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>0.8125</v>
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="AK17" s="8" t="n">
         <v>0.8958333333333334</v>
@@ -11065,7 +11065,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="AD18" s="8" t="n">
         <v>0.7916666666666666</v>
@@ -11223,7 +11223,7 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK18" s="8" t="n">
         <v>0.78125</v>
@@ -11251,7 +11251,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>0.59375</v>
@@ -11441,7 +11441,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45814</v>
+        <v>45815</v>
       </c>
       <c r="AD20" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45905</v>
+        <v>45906</v>
       </c>
       <c r="AD21" s="8" t="n">
         <v>0.65625</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="AK21" s="8" t="n">
         <v>0.6666666666666666</v>
@@ -11822,7 +11822,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AD22" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="AK22" s="8" t="n">
         <v>0.6979166666666666</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45970</v>
+        <v>45971</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>0.8854166666666666</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -12194,7 +12194,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AD24" s="8" t="n">
         <v>0.7708333333333334</v>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AK24" s="8" t="n">
         <v>0.6666666666666666</v>
@@ -12381,7 +12381,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>0.875</v>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>0.71875</v>
@@ -12567,7 +12567,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="AD26" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
-        <v>45961</v>
+        <v>45962</v>
       </c>
       <c r="AK26" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -12753,7 +12753,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="AD27" s="8" t="n">
         <v>0.90625</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="AK27" s="8" t="n">
         <v>0.8020833333333334</v>
@@ -12944,7 +12944,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45591</v>
+        <v>45592</v>
       </c>
       <c r="AD28" s="8" t="n">
         <v>0.4583333333333333</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="AK28" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45830</v>
+        <v>45831</v>
       </c>
       <c r="AD29" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -13296,7 +13296,7 @@
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>0.4895833333333333</v>
@@ -13328,7 +13328,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45722</v>
+        <v>45723</v>
       </c>
       <c r="AD30" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -13522,7 +13522,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="AK31" s="8" t="n">
         <v>0.46875</v>
@@ -13721,7 +13721,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="AD32" s="8" t="n">
         <v>0.3020833333333333</v>
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK32" s="8" t="n">
         <v>0.4375</v>
@@ -13911,7 +13911,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45759</v>
+        <v>45760</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="AD33" s="8" t="n">
         <v>0.90625</v>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="AK33" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -16172,7 +16172,8 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
+          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
+Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16678,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
